--- a/grupos/4APV - Estadisticos 20232.xlsx
+++ b/grupos/4APV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -158,16 +158,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
+    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Urias Morales Alejandra</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Sanchez Hernández Raymundo</t>
@@ -176,9 +179,6 @@
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -191,49 +191,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
   </si>
   <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
+    <t>GUILLERMO SAUL</t>
   </si>
 </sst>
 </file>
@@ -760,25 +742,25 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -805,22 +787,22 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -849,25 +831,25 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -891,13 +873,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>10</v>
@@ -906,10 +888,10 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -938,25 +920,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -986,16 +968,16 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z6">
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1027,25 +1009,25 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1069,10 +1051,10 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1081,13 +1063,13 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1116,25 +1098,25 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1161,7 +1143,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1170,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>7</v>
@@ -1196,16 +1178,16 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1223,13 +1205,13 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1258,25 +1240,25 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1300,16 +1282,16 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1318,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1347,25 +1329,25 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1389,16 +1371,16 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1407,7 +1389,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1436,25 +1418,25 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1487,7 +1469,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1525,25 +1507,25 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1570,19 +1552,19 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -1614,25 +1596,25 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1659,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1671,7 +1653,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -1703,25 +1685,25 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1748,7 +1730,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1760,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1792,25 +1774,25 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1837,13 +1819,13 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>9</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -1881,25 +1863,25 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1923,25 +1905,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -1970,25 +1952,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2015,19 +1997,19 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>10</v>
@@ -2059,25 +2041,25 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2104,19 +2086,19 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2148,25 +2130,25 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2190,25 +2172,25 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2237,25 +2219,25 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2279,25 +2261,25 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2323,22 +2305,22 @@
         <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2371,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2403,25 +2385,25 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2445,16 +2427,16 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2492,25 +2474,25 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2537,19 +2519,19 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>8</v>
@@ -2706,16 +2688,16 @@
         <v>95</v>
       </c>
       <c r="J4">
-        <v>95.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K4">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -2727,16 +2709,16 @@
         <v>95</v>
       </c>
       <c r="Q4">
-        <v>95.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R4">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -2777,10 +2759,10 @@
         <v>95.7</v>
       </c>
       <c r="K5">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -2798,10 +2780,10 @@
         <v>95.7</v>
       </c>
       <c r="R5">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -2845,16 +2827,16 @@
         <v>95.7</v>
       </c>
       <c r="K6">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L6">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2866,16 +2848,16 @@
         <v>95.7</v>
       </c>
       <c r="R6">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="S6">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2907,43 +2889,43 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J7">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K7">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="L7">
         <v>82.90000000000001</v>
       </c>
       <c r="M7">
+        <v>83.3</v>
+      </c>
+      <c r="N7">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
         <v>85</v>
       </c>
-      <c r="N7">
-        <v>95</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>75</v>
-      </c>
       <c r="Q7">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R7">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="S7">
         <v>82.90000000000001</v>
       </c>
       <c r="T7">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U7">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -2978,19 +2960,19 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="K8">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="L8">
         <v>91.40000000000001</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2999,19 +2981,19 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="R8">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="S8">
         <v>91.40000000000001</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3037,25 +3019,25 @@
         <v>95</v>
       </c>
       <c r="J9">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L9">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P9">
         <v>95</v>
       </c>
       <c r="Q9">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S9">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3090,7 +3072,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3111,7 +3093,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3158,7 +3140,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3179,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3220,43 +3202,43 @@
         <v>81.3</v>
       </c>
       <c r="I12">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="J12">
-        <v>95.7</v>
+        <v>91.5</v>
       </c>
       <c r="K12">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="L12">
-        <v>82.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="M12">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="N12">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="O12">
         <v>81.3</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q12">
-        <v>95.7</v>
+        <v>91.5</v>
       </c>
       <c r="R12">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="S12">
-        <v>82.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="T12">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U12">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="V12">
         <v>81.3</v>
@@ -3365,10 +3347,10 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -3386,10 +3368,10 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -3424,46 +3406,46 @@
         <v>81.3</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J15">
         <v>95.7</v>
       </c>
       <c r="K15">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="L15">
-        <v>25.7</v>
+        <v>54.3</v>
       </c>
       <c r="M15">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O15">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="Q15">
         <v>95.7</v>
       </c>
       <c r="R15">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="S15">
-        <v>25.7</v>
+        <v>54.3</v>
       </c>
       <c r="T15">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U15">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V15">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3495,16 +3477,16 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -3516,16 +3498,16 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -3569,13 +3551,13 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3590,13 +3572,13 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="T17">
         <v>100</v>
       </c>
       <c r="U17">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -3696,7 +3678,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -3705,7 +3687,7 @@
         <v>90</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -3717,7 +3699,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -3726,7 +3708,7 @@
         <v>90</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -3764,10 +3746,10 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J20">
-        <v>95.7</v>
+        <v>91.5</v>
       </c>
       <c r="K20">
         <v>93.3</v>
@@ -3776,19 +3758,19 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q20">
-        <v>95.7</v>
+        <v>91.5</v>
       </c>
       <c r="R20">
         <v>93.3</v>
@@ -3797,10 +3779,10 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -3835,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -3844,7 +3826,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -3856,7 +3838,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -3865,7 +3847,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -3900,7 +3882,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -3909,7 +3891,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -3918,7 +3900,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>95.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -3927,7 +3909,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -3959,46 +3941,46 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="J23">
-        <v>95.7</v>
+        <v>46.8</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L23">
-        <v>85.7</v>
+        <v>42.9</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="N23">
-        <v>90</v>
+        <v>43.9</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P23">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="Q23">
-        <v>95.7</v>
+        <v>46.8</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="S23">
-        <v>85.7</v>
+        <v>42.9</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="U23">
-        <v>90</v>
+        <v>43.9</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4042,7 +4024,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4063,7 +4045,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4123,7 +4105,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -4132,19 +4114,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>57.1</v>
+        <v>76.2</v>
       </c>
       <c r="G2" s="2">
-        <v>42.9</v>
+        <v>23.8</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4155,7 +4137,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -4164,19 +4146,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>61.9</v>
+        <v>76.2</v>
       </c>
       <c r="G3" s="2">
-        <v>38.1</v>
+        <v>23.8</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4187,28 +4169,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>21.1</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4219,28 +4201,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>78.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="G5" s="2">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4251,28 +4233,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>85</v>
+        <v>85.7</v>
       </c>
       <c r="G6" s="2">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4283,28 +4265,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>90.5</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4315,7 +4297,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>52</v>
@@ -4324,19 +4306,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="G8" s="2">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4386,7 +4368,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4418,22 +4400,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4441,22 +4423,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>21330051920117</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4464,22 +4446,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920395</v>
+        <v>21330051920396</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4487,93 +4469,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920395</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920117</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920272</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920288</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20232.xlsx
+++ b/grupos/4APV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="64">
   <si>
     <t>Materia</t>
   </si>
@@ -158,27 +158,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>Urias Morales Alejandra</t>
+  </si>
+  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Urias Morales Alejandra</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Sanchez Hernández Raymundo</t>
   </si>
   <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -191,28 +191,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>GUILLERMO SAUL</t>
@@ -763,28 +757,28 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -796,13 +790,13 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -852,40 +846,40 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -941,31 +935,31 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1030,40 +1024,40 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1119,31 +1113,31 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1152,13 +1146,13 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1190,28 +1184,28 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1261,25 +1255,25 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1300,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1350,28 +1344,28 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1389,7 +1383,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1439,28 +1433,28 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1472,10 +1466,10 @@
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1528,25 +1522,25 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1617,25 +1611,25 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1706,25 +1700,25 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1795,25 +1789,25 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1884,25 +1878,25 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1917,13 +1911,13 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -1973,31 +1967,31 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2006,13 +2000,13 @@
         <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2062,25 +2056,25 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2092,16 +2086,16 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>8</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2151,28 +2145,28 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2184,7 +2178,7 @@
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB20">
         <v>6</v>
@@ -2240,28 +2234,28 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2270,16 +2264,16 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2323,40 +2317,40 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2406,37 +2400,37 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2495,31 +2489,31 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2531,7 +2525,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>8</v>
@@ -2706,22 +2700,22 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q4">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="R4">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T4">
-        <v>94.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -2774,22 +2768,22 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R5">
-        <v>95</v>
+        <v>87.8</v>
       </c>
       <c r="S5">
-        <v>98.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -2845,19 +2839,19 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R6">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S6">
-        <v>94.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T6">
-        <v>97.2</v>
+        <v>95.8</v>
       </c>
       <c r="U6">
-        <v>97.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2910,22 +2904,22 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>85</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q7">
-        <v>93.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R7">
-        <v>70</v>
+        <v>77.8</v>
       </c>
       <c r="S7">
-        <v>82.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="T7">
         <v>83.3</v>
       </c>
       <c r="U7">
-        <v>95.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -2978,22 +2972,22 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q8">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R8">
-        <v>91.7</v>
+        <v>93.3</v>
       </c>
       <c r="S8">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T8">
-        <v>97.2</v>
+        <v>93.8</v>
       </c>
       <c r="U8">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3028,16 +3022,16 @@
         <v>92.90000000000001</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q9">
-        <v>93.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R9">
-        <v>98.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S9">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3093,7 +3087,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3161,7 +3155,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3223,22 +3217,22 @@
         <v>81.3</v>
       </c>
       <c r="P12">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q12">
-        <v>91.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="R12">
-        <v>91.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="S12">
-        <v>80</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="T12">
         <v>83.3</v>
       </c>
       <c r="U12">
-        <v>92.7</v>
+        <v>90.5</v>
       </c>
       <c r="V12">
         <v>81.3</v>
@@ -3368,10 +3362,10 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T14">
-        <v>97.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -3427,25 +3421,25 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P15">
-        <v>65</v>
+        <v>56.3</v>
       </c>
       <c r="Q15">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R15">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="S15">
-        <v>54.3</v>
+        <v>50</v>
       </c>
       <c r="T15">
         <v>83.3</v>
       </c>
       <c r="U15">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="V15">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3498,19 +3492,19 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T16">
-        <v>97.2</v>
+        <v>95.8</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -3572,13 +3566,13 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="T17">
         <v>100</v>
       </c>
       <c r="U17">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -3640,13 +3634,13 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -3699,22 +3693,22 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="S19">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T19">
         <v>100</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -3767,25 +3761,25 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q20">
-        <v>91.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="R20">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T20">
         <v>83.3</v>
       </c>
       <c r="U20">
-        <v>97.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="V20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3838,19 +3832,19 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>93.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T21">
-        <v>97.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -3900,7 +3894,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>93.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -3909,10 +3903,10 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>97.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -3962,25 +3956,25 @@
         <v>50</v>
       </c>
       <c r="P23">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="Q23">
-        <v>46.8</v>
+        <v>32.4</v>
       </c>
       <c r="R23">
-        <v>70</v>
+        <v>46.7</v>
       </c>
       <c r="S23">
-        <v>42.9</v>
+        <v>26.8</v>
       </c>
       <c r="T23">
-        <v>91.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="U23">
-        <v>43.9</v>
+        <v>33.3</v>
       </c>
       <c r="V23">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4033,19 +4027,19 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T24">
         <v>100</v>
       </c>
       <c r="U24">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4105,28 +4099,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>76.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>23.8</v>
+        <v>21.1</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4137,7 +4131,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -4146,19 +4140,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>76.2</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>23.8</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4169,28 +4163,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>78.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G4" s="2">
-        <v>21.1</v>
+        <v>14.3</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4210,19 +4204,19 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4233,7 +4227,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -4242,19 +4236,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="G6" s="2">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4265,25 +4259,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="G7" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="H7">
         <v>7.5</v>
@@ -4297,28 +4291,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>52</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="G8" s="2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4368,7 +4362,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4400,19 +4394,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920117</v>
+        <v>22330051920405</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>47</v>
@@ -4423,22 +4417,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920117</v>
+        <v>22330051920405</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4446,19 +4440,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>47</v>
@@ -4469,24 +4463,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>46</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920402</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
